--- a/product_upload/packages/7/file.xlsx
+++ b/product_upload/packages/7/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR101"/>
+  <dimension ref="A1:AS101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -639,6 +639,11 @@
         </is>
       </c>
       <c r="AR1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -667,7 +672,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -812,6 +817,11 @@
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>TRISORALEN TABLET 5MG</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>SKU-F04002AFB9C2</t>
         </is>
       </c>
@@ -839,7 +849,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -996,6 +1006,11 @@
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr">
         <is>
+          <t>TYPHM VI CAPSULAR POLYSACCHRIDE SD.SYRIN</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>SKU-AF65BF1229E7</t>
         </is>
       </c>
@@ -1023,7 +1038,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1176,6 +1191,11 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
+          <t>ULTRA-K SYRUP</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>SKU-CCBE8D4377B0</t>
         </is>
       </c>
@@ -1203,7 +1223,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1356,6 +1376,11 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
+          <t>ULTRADERM</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
           <t>SKU-17750C8B4CCF</t>
         </is>
       </c>
@@ -1383,7 +1408,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1536,6 +1561,11 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>ULTRADERM</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
           <t>SKU-72E402C3E2ED</t>
         </is>
       </c>
@@ -1563,7 +1593,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1716,6 +1746,11 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>ULTRACEF 500MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
           <t>SKU-F8DE2C81E1EA</t>
         </is>
       </c>
@@ -1743,7 +1778,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1896,6 +1931,11 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>UCIDERM -B CREAM</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
           <t>SKU-863915F8E871</t>
         </is>
       </c>
@@ -1923,7 +1963,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2076,6 +2116,11 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
+          <t>UCIDERM 2% W-W GEL</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
           <t>SKU-0993544909E4</t>
         </is>
       </c>
@@ -2103,7 +2148,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2252,6 +2297,11 @@
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>UCIDERM 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
           <t>SKU-31F46BF86F0B</t>
         </is>
       </c>
@@ -2279,7 +2329,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2424,6 +2474,11 @@
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>UCIDERM 2 % CREAM</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
           <t>SKU-38951B98BAB8</t>
         </is>
       </c>
@@ -2451,7 +2506,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2608,6 +2663,11 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>U-CEF 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
           <t>SKU-D2EBDAEEB0C5</t>
         </is>
       </c>
@@ -2635,7 +2695,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2784,6 +2844,11 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>ULTRACEF 250MG PWD.FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
           <t>SKU-D9D6C43E275C</t>
         </is>
       </c>
@@ -2811,7 +2876,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2960,6 +3025,11 @@
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>TRISORALEN TABLET 5MG</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
           <t>SKU-7A39AA7C8B2C</t>
         </is>
       </c>
@@ -2987,7 +3057,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3144,6 +3214,11 @@
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>VALCYTE 450MG FILM - COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
           <t>SKU-8B6E663E5405</t>
         </is>
       </c>
@@ -3171,7 +3246,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3320,6 +3395,11 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>VERO 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
           <t>SKU-95E3769B5A17</t>
         </is>
       </c>
@@ -3347,7 +3427,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3496,6 +3576,11 @@
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>VERO 50 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
           <t>SKU-84BF541C6287</t>
         </is>
       </c>
@@ -3523,7 +3608,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3676,6 +3761,11 @@
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>VERMOX SUSPN 2%</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
           <t>SKU-E1E458EF20A0</t>
         </is>
       </c>
@@ -3703,7 +3793,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3860,6 +3950,11 @@
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>VERMOX 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
           <t>SKU-F052CCDDD34D</t>
         </is>
       </c>
@@ -3887,7 +3982,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4040,6 +4135,11 @@
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>VERINE SR 200MG SUSTAINED RELEASED CAP</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
           <t>SKU-3A7CD53DAFE0</t>
         </is>
       </c>
@@ -4067,7 +4167,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4220,6 +4320,11 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>VERINE 135MG TAB</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
           <t>SKU-EAD8E2C9EF3D</t>
         </is>
       </c>
@@ -4247,7 +4352,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4404,6 +4509,11 @@
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>VENTOLIN RESPIRATORY SOLUTIN</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>SKU-4902AE96E88F</t>
         </is>
       </c>
@@ -4431,7 +4541,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4588,6 +4698,11 @@
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>VENTOLIN EVOHALER</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
           <t>SKU-0DE6404265D9</t>
         </is>
       </c>
@@ -4615,7 +4730,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4772,6 +4887,11 @@
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>VERSATIS 5% MEDICATED PLASTER</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
           <t>SKU-F817ED2BB411</t>
         </is>
       </c>
@@ -4799,7 +4919,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4964,6 +5084,11 @@
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr">
         <is>
+          <t>VERSATIS 5% MEDICATED PLASTER</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
           <t>SKU-DE50E76C2215</t>
         </is>
       </c>
@@ -4991,7 +5116,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5152,6 +5277,11 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
+          <t>VESICARE 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
           <t>SKU-27735F941567</t>
         </is>
       </c>
@@ -5179,7 +5309,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5336,6 +5466,11 @@
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="inlineStr">
         <is>
+          <t>VESICARE 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
           <t>SKU-F29B2F80D856</t>
         </is>
       </c>
@@ -5363,7 +5498,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5530,6 +5665,11 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
+          <t>VICTOZA 6MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
           <t>SKU-0F7BE2A77918</t>
         </is>
       </c>
@@ -5557,7 +5697,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5702,6 +5842,11 @@
       <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="inlineStr">
         <is>
+          <t>VICKS VAPORUB OINT</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
           <t>SKU-AEC47D644CBA</t>
         </is>
       </c>
@@ -5729,7 +5874,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5882,6 +6027,11 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
+          <t>VICKS VAPORUB OINTCamphor</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
           <t>SKU-3547EFCA472F</t>
         </is>
       </c>
@@ -5909,7 +6059,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6054,6 +6204,11 @@
       <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr">
         <is>
+          <t>VICKS INHALER 0.014 OZ</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>SKU-9DF846DCB34C</t>
         </is>
       </c>
@@ -6081,7 +6236,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6226,6 +6381,11 @@
       <c r="AQ32" t="inlineStr"/>
       <c r="AR32" t="inlineStr">
         <is>
+          <t>VICKS DAY QUIL ALCOHOL FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
           <t>SKU-DF2637C03888</t>
         </is>
       </c>
@@ -6253,7 +6413,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6410,6 +6570,11 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
+          <t>VICKS 44 E PEDIATRIC ALCOHOL FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
           <t>SKU-011B10875D57</t>
         </is>
       </c>
@@ -6437,7 +6602,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6586,6 +6751,11 @@
       <c r="AQ34" t="inlineStr"/>
       <c r="AR34" t="inlineStr">
         <is>
+          <t>VICKS SINEX NASAL SPRAY.</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
           <t>SKU-7C996B5B15E1</t>
         </is>
       </c>
@@ -6613,7 +6783,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6774,6 +6944,11 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
+          <t>VIAGRA 50MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
           <t>SKU-E4564C8B2AF5</t>
         </is>
       </c>
@@ -6801,7 +6976,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6958,6 +7133,11 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>VIAGRA 25MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
           <t>SKU-3C6ABD3A6654</t>
         </is>
       </c>
@@ -6985,7 +7165,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7138,6 +7318,11 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr">
         <is>
+          <t>VIAGRA 100MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
           <t>SKU-20E4848D412E</t>
         </is>
       </c>
@@ -7165,7 +7350,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7320,6 +7505,11 @@
       <c r="AQ38" t="inlineStr"/>
       <c r="AR38" t="inlineStr">
         <is>
+          <t>VEXAL XR 75 MG EXTENDED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
           <t>SKU-77780A6AB41F</t>
         </is>
       </c>
@@ -7347,7 +7537,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7506,6 +7696,11 @@
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr">
         <is>
+          <t>VEXAL XR 37.5 MG EXTENDED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
           <t>SKU-09B3E0332D8A</t>
         </is>
       </c>
@@ -7533,7 +7728,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7688,6 +7883,11 @@
       <c r="AQ40" t="inlineStr"/>
       <c r="AR40" t="inlineStr">
         <is>
+          <t>VEXAL XR 150 MG EXTENDED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
           <t>SKU-17F1EC9ADA94</t>
         </is>
       </c>
@@ -7715,7 +7915,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7876,6 +8076,11 @@
       <c r="AQ41" t="inlineStr"/>
       <c r="AR41" t="inlineStr">
         <is>
+          <t>VALDOXAN 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
           <t>SKU-E2AE013AECFB</t>
         </is>
       </c>
@@ -7903,7 +8108,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8052,6 +8257,11 @@
       <c r="AQ42" t="inlineStr"/>
       <c r="AR42" t="inlineStr">
         <is>
+          <t>VENTOLIN</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
           <t>SKU-AF547EBDFD52</t>
         </is>
       </c>
@@ -8079,7 +8289,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8236,6 +8446,11 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
+          <t>VAQTA VACCINE 50 U VIAL</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
           <t>SKU-F7BCB051BACE</t>
         </is>
       </c>
@@ -8263,7 +8478,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8420,6 +8635,11 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
+          <t>VAQTA 25U SYRINGE I.M</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
           <t>SKU-714592AC77DF</t>
         </is>
       </c>
@@ -8447,7 +8667,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8608,6 +8828,11 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
+          <t>VALTREX</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
           <t>SKU-1358D3B45126</t>
         </is>
       </c>
@@ -8635,7 +8860,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8796,6 +9021,11 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
+          <t>VALTREX</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
           <t>SKU-4EC2064EB629</t>
         </is>
       </c>
@@ -8823,7 +9053,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8980,6 +9210,11 @@
       <c r="AQ47" t="inlineStr"/>
       <c r="AR47" t="inlineStr">
         <is>
+          <t>VALOPRA 57.64 MG-ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
           <t>SKU-AD805F03589A</t>
         </is>
       </c>
@@ -9007,7 +9242,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9156,6 +9391,11 @@
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr">
         <is>
+          <t>VALOPRA 200 MG-ML SOLUTION</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
           <t>SKU-78A9AA2BA271</t>
         </is>
       </c>
@@ -9183,7 +9423,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9332,6 +9572,11 @@
       <c r="AQ49" t="inlineStr"/>
       <c r="AR49" t="inlineStr">
         <is>
+          <t>VALONTAN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
           <t>SKU-865BE61D96C3</t>
         </is>
       </c>
@@ -9359,7 +9604,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9520,6 +9765,11 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
+          <t>VALIUM TAB 5MG</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
           <t>SKU-5F370C86CC8C</t>
         </is>
       </c>
@@ -9547,7 +9797,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9704,6 +9954,11 @@
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr">
         <is>
+          <t>VALIUM TAB 2 MG</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
           <t>SKU-DEB6E1EB041E</t>
         </is>
       </c>
@@ -9731,7 +9986,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9892,6 +10147,11 @@
       </c>
       <c r="AR52" t="inlineStr">
         <is>
+          <t>VALIUM TAB 10 MG</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
           <t>SKU-F0CBE4135FAC</t>
         </is>
       </c>
@@ -9919,7 +10179,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10076,6 +10336,11 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr">
         <is>
+          <t>VASCODIPINE</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
           <t>SKU-01BE6E8F4D5A</t>
         </is>
       </c>
@@ -10103,7 +10368,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10264,6 +10529,11 @@
       </c>
       <c r="AR54" t="inlineStr">
         <is>
+          <t>VASCODIPINE</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
           <t>SKU-58AE100D46AA</t>
         </is>
       </c>
@@ -10291,7 +10561,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10448,6 +10718,11 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr">
         <is>
+          <t>VASCODIPINE</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
           <t>SKU-81C364709B57</t>
         </is>
       </c>
@@ -10475,7 +10750,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10636,6 +10911,11 @@
       </c>
       <c r="AR56" t="inlineStr">
         <is>
+          <t>VENEX XR 75MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
           <t>SKU-08A8546C4B15</t>
         </is>
       </c>
@@ -10663,7 +10943,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10824,6 +11104,11 @@
       </c>
       <c r="AR57" t="inlineStr">
         <is>
+          <t>VENEX XR 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
           <t>SKU-4FB83B7F4526</t>
         </is>
       </c>
@@ -10851,7 +11136,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10996,6 +11281,11 @@
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="inlineStr">
         <is>
+          <t>VENORUTON 300MG CAP</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
           <t>SKU-42500BEF9043</t>
         </is>
       </c>
@@ -11023,7 +11313,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11176,6 +11466,11 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
+          <t>VAVO 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
           <t>SKU-4DAAFCCF13A2</t>
         </is>
       </c>
@@ -11203,7 +11498,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11360,6 +11655,11 @@
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr">
         <is>
+          <t>VASTA 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
           <t>SKU-C22640F16E17</t>
         </is>
       </c>
@@ -11387,7 +11687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11548,6 +11848,11 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
+          <t>VASTA 20MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
           <t>SKU-F0D349915016</t>
         </is>
       </c>
@@ -11575,7 +11880,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11732,6 +12037,11 @@
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr">
         <is>
+          <t>VASTA 10MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
           <t>SKU-C90D99F550CE</t>
         </is>
       </c>
@@ -11759,7 +12069,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11926,6 +12236,11 @@
       </c>
       <c r="AR63" t="inlineStr">
         <is>
+          <t>VASTAREL MR 35MG MODIFIED RELEASE TABLET</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
           <t>SKU-FE5AE6F9F6CB</t>
         </is>
       </c>
@@ -11953,7 +12268,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12106,6 +12421,11 @@
       <c r="AQ64" t="inlineStr"/>
       <c r="AR64" t="inlineStr">
         <is>
+          <t>TRIPOFED SYRUP</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
           <t>SKU-60FC26C69B10</t>
         </is>
       </c>
@@ -12133,7 +12453,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12294,6 +12614,11 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr">
         <is>
+          <t>TRIPOFED DM SYRUP</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
           <t>SKU-3A39D01CE98B</t>
         </is>
       </c>
@@ -12321,7 +12646,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12478,6 +12803,11 @@
       <c r="AQ66" t="inlineStr"/>
       <c r="AR66" t="inlineStr">
         <is>
+          <t>TEGRETOL TAB 200MG</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
           <t>SKU-627886205409</t>
         </is>
       </c>
@@ -12505,7 +12835,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12666,6 +12996,11 @@
       </c>
       <c r="AR67" t="inlineStr">
         <is>
+          <t>TEGRETOL 2% oral suspension</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
           <t>SKU-F005CD6402DB</t>
         </is>
       </c>
@@ -12693,7 +13028,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12854,6 +13189,11 @@
       </c>
       <c r="AR68" t="inlineStr">
         <is>
+          <t>TEGRETOL CR 400MG SCORED TAB</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
           <t>SKU-D63C17948F6D</t>
         </is>
       </c>
@@ -12881,7 +13221,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13034,6 +13374,11 @@
       </c>
       <c r="AR69" t="inlineStr">
         <is>
+          <t>TERRELL 100% VAPOUR LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
           <t>SKU-9396D7E95DBD</t>
         </is>
       </c>
@@ -13061,7 +13406,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13210,6 +13555,11 @@
       <c r="AQ70" t="inlineStr"/>
       <c r="AR70" t="inlineStr">
         <is>
+          <t>TERFINA CREAM</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
           <t>SKU-EFB5A4DBC9A8</t>
         </is>
       </c>
@@ -13237,7 +13587,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13394,6 +13744,11 @@
       <c r="AQ71" t="inlineStr"/>
       <c r="AR71" t="inlineStr">
         <is>
+          <t>TENORMIN TAB 50MG</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
           <t>SKU-7F21B2CFD882</t>
         </is>
       </c>
@@ -13421,7 +13776,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13582,6 +13937,11 @@
       </c>
       <c r="AR72" t="inlineStr">
         <is>
+          <t>TENORMIN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
           <t>SKU-0729B367F55C</t>
         </is>
       </c>
@@ -13609,7 +13969,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13770,6 +14130,11 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
+          <t>TENORETIC TAB</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
           <t>SKU-9C00F32E04F3</t>
         </is>
       </c>
@@ -13797,7 +14162,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13954,6 +14319,11 @@
       <c r="AQ74" t="inlineStr"/>
       <c r="AR74" t="inlineStr">
         <is>
+          <t>TENORMIN TAB 100MG</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
           <t>SKU-3EBE6C2AFE00</t>
         </is>
       </c>
@@ -13981,7 +14351,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14138,6 +14508,11 @@
       <c r="AQ75" t="inlineStr"/>
       <c r="AR75" t="inlineStr">
         <is>
+          <t>TABUVAN 160 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
           <t>SKU-C68EB02D1FE0</t>
         </is>
       </c>
@@ -14165,7 +14540,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14326,6 +14701,11 @@
       </c>
       <c r="AR76" t="inlineStr">
         <is>
+          <t>TABUNEX 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
           <t>SKU-CD89D054C602</t>
         </is>
       </c>
@@ -14353,7 +14733,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14502,6 +14882,11 @@
       <c r="AQ77" t="inlineStr"/>
       <c r="AR77" t="inlineStr">
         <is>
+          <t>TABUFLU 75MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
           <t>SKU-EACF98CA0770</t>
         </is>
       </c>
@@ -14529,7 +14914,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14690,6 +15075,11 @@
       </c>
       <c r="AR78" t="inlineStr">
         <is>
+          <t>TABOCINE 100</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
           <t>SKU-640C76E834C3</t>
         </is>
       </c>
@@ -14717,7 +15107,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14866,6 +15256,11 @@
       <c r="AQ79" t="inlineStr"/>
       <c r="AR79" t="inlineStr">
         <is>
+          <t>TABIXA 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
           <t>SKU-F1B99E94F352</t>
         </is>
       </c>
@@ -14893,7 +15288,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15042,6 +15437,11 @@
       <c r="AQ80" t="inlineStr"/>
       <c r="AR80" t="inlineStr">
         <is>
+          <t>TABIVIR 300MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
           <t>SKU-DF3A6A4E3093</t>
         </is>
       </c>
@@ -15069,7 +15469,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15222,6 +15622,11 @@
       </c>
       <c r="AR81" t="inlineStr">
         <is>
+          <t>TABIVIR 150MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
           <t>SKU-B9076AC189BB</t>
         </is>
       </c>
@@ -15249,7 +15654,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15406,6 +15811,11 @@
       <c r="AQ82" t="inlineStr"/>
       <c r="AR82" t="inlineStr">
         <is>
+          <t>TABIFLEX COOL 1% GEL</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
           <t>SKU-9579756BDB26</t>
         </is>
       </c>
@@ -15433,7 +15843,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15586,6 +15996,11 @@
       </c>
       <c r="AR83" t="inlineStr">
         <is>
+          <t>TABIFLEX 50MG E.C.TAB</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
           <t>SKU-A30E5222A30E</t>
         </is>
       </c>
@@ -15613,7 +16028,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15766,6 +16181,11 @@
       </c>
       <c r="AR84" t="inlineStr">
         <is>
+          <t>TABICLOR MR 750MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
           <t>SKU-7B98E7E959FF</t>
         </is>
       </c>
@@ -15793,7 +16213,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15946,6 +16366,11 @@
       </c>
       <c r="AR85" t="inlineStr">
         <is>
+          <t>TABICLOR 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
           <t>SKU-4BC11EAE8978</t>
         </is>
       </c>
@@ -15973,7 +16398,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16122,6 +16547,11 @@
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr">
         <is>
+          <t>TABICLOR 375 MG- 5ML ORAL SUSPNSION</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
           <t>SKU-3146C6E256C3</t>
         </is>
       </c>
@@ -16149,7 +16579,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16298,6 +16728,11 @@
       <c r="AQ87" t="inlineStr"/>
       <c r="AR87" t="inlineStr">
         <is>
+          <t>TABICLOR 250MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
           <t>SKU-BBF0015A5DFF</t>
         </is>
       </c>
@@ -16325,7 +16760,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16474,6 +16909,11 @@
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="inlineStr">
         <is>
+          <t>TABICLOR 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
           <t>SKU-5D667561A4A3</t>
         </is>
       </c>
@@ -16501,7 +16941,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16664,6 +17104,11 @@
       </c>
       <c r="AR89" t="inlineStr">
         <is>
+          <t>TABETA 0.1%SCALP APPLICATION</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
           <t>SKU-47FDA7A80255</t>
         </is>
       </c>
@@ -16691,7 +17136,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16844,6 +17289,11 @@
       <c r="AQ90" t="inlineStr"/>
       <c r="AR90" t="inlineStr">
         <is>
+          <t>TABUVAN 320 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
           <t>SKU-8CCA21493EBF</t>
         </is>
       </c>
@@ -16871,7 +17321,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17028,6 +17478,11 @@
       <c r="AQ91" t="inlineStr"/>
       <c r="AR91" t="inlineStr">
         <is>
+          <t>TABUVAN 40 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
           <t>SKU-4B0185CE9EF1</t>
         </is>
       </c>
@@ -17055,7 +17510,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17212,6 +17667,11 @@
       <c r="AQ92" t="inlineStr"/>
       <c r="AR92" t="inlineStr">
         <is>
+          <t>TABUVAN 80 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
           <t>SKU-2ECFA2FD6AAF</t>
         </is>
       </c>
@@ -17239,7 +17699,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17392,6 +17852,11 @@
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="inlineStr">
         <is>
+          <t>TachoSil sealant matrix</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
           <t>SKU-077119FE3FF9</t>
         </is>
       </c>
@@ -17419,7 +17884,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17578,6 +18043,11 @@
       <c r="AQ94" t="inlineStr"/>
       <c r="AR94" t="inlineStr">
         <is>
+          <t>TAVANIC 500MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
           <t>SKU-5D0F3294AD58</t>
         </is>
       </c>
@@ -17605,7 +18075,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17750,6 +18220,11 @@
       <c r="AQ95" t="inlineStr"/>
       <c r="AR95" t="inlineStr">
         <is>
+          <t>TAMIFLU 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
           <t>SKU-479D6A8AA032</t>
         </is>
       </c>
@@ -17777,7 +18252,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17930,6 +18405,11 @@
       </c>
       <c r="AR96" t="inlineStr">
         <is>
+          <t>TAMBOCOR 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
           <t>SKU-528D63677917</t>
         </is>
       </c>
@@ -17957,7 +18437,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18114,6 +18594,11 @@
       <c r="AQ97" t="inlineStr"/>
       <c r="AR97" t="inlineStr">
         <is>
+          <t>TAKEPRON 30MG CAPS</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
           <t>SKU-C513BB69A972</t>
         </is>
       </c>
@@ -18141,7 +18626,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18298,6 +18783,11 @@
       <c r="AQ98" t="inlineStr"/>
       <c r="AR98" t="inlineStr">
         <is>
+          <t>TAKEPRON 15MG CAP.</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
           <t>SKU-005D8DD83AD7</t>
         </is>
       </c>
@@ -18325,7 +18815,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18486,6 +18976,11 @@
       <c r="AQ99" t="inlineStr"/>
       <c r="AR99" t="inlineStr">
         <is>
+          <t>TRIPOFED EXPECTORANT SYRUP</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
           <t>SKU-020FAD1EA053</t>
         </is>
       </c>
@@ -18513,7 +19008,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18672,6 +19167,11 @@
       <c r="AQ100" t="inlineStr"/>
       <c r="AR100" t="inlineStr">
         <is>
+          <t>TEVETEN 600MG TAB</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
           <t>SKU-65D8F4A2B842</t>
         </is>
       </c>
@@ -18699,7 +19199,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18855,6 +19355,11 @@
       </c>
       <c r="AQ101" t="inlineStr"/>
       <c r="AR101" t="inlineStr">
+        <is>
+          <t>TRACLEER 62.5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
         <is>
           <t>SKU-6A8EDD623A8C</t>
         </is>
@@ -18871,7 +19376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18917,100 +19422,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19042,7 +19552,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19057,92 +19567,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-94661</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>64.41</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>696</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19174,7 +19689,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19189,92 +19704,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-43696</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>322.67</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>697</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19306,7 +19826,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19321,92 +19841,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-85619</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>366.77</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>698</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19438,7 +19963,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19453,92 +19978,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-96387</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>396.95</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>699</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19570,7 +20100,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19585,92 +20115,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-94532</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>60.78</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>700</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19702,7 +20237,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19717,92 +20252,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-58663</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>40.8</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>701</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19834,7 +20374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19849,92 +20389,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-52813</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>433.07</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Health Trackers</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>702</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19966,7 +20511,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19981,92 +20526,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-93532</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>76.22</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>703</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20098,7 +20648,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20113,92 +20663,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-91116</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>381.75</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>704</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20230,7 +20785,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20245,92 +20800,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-89788</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>90.48999999999999</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>705</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20362,7 +20922,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20377,92 +20937,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-66215</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>495.3</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>706</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20494,7 +21059,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20509,92 +21074,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-76119</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>147.78</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>707</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20611,7 +21181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20717,6 +21287,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20752,7 +21332,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20817,6 +21397,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-19636A66C658</t>
         </is>
@@ -20853,7 +21443,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20918,6 +21508,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-84E942455D64</t>
         </is>
@@ -20954,7 +21554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21019,6 +21619,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-16CD00DE0557</t>
         </is>
@@ -21055,7 +21665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21120,6 +21730,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-58A502061BFD</t>
         </is>
@@ -21156,7 +21776,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21221,6 +21841,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-59ECCDE298FD</t>
         </is>
@@ -21257,7 +21887,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21322,6 +21952,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-BBDC8BD1E523</t>
         </is>
@@ -21358,7 +21998,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21423,6 +22063,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-443788E5E988</t>
         </is>
@@ -21459,7 +22109,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21524,6 +22174,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-82B7B7580950</t>
         </is>
@@ -21560,7 +22220,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21625,6 +22285,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-C5608D94961D</t>
         </is>
@@ -21661,7 +22331,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21726,6 +22396,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-3359E601FEB5</t>
         </is>
@@ -21762,7 +22442,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21827,6 +22507,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-D84FF2C224FA</t>
         </is>
@@ -21863,7 +22553,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21928,6 +22618,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-E09800AA7139</t>
         </is>
@@ -21964,7 +22664,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22029,6 +22729,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-7244BD93DD9F</t>
         </is>
@@ -22065,7 +22775,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22130,6 +22840,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-7E389C103DB2</t>
         </is>
@@ -22166,7 +22886,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22231,6 +22951,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-2B26093B1A96</t>
         </is>
@@ -22267,7 +22997,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22332,6 +23062,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-B70C728C4456</t>
         </is>
@@ -22368,7 +23108,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22433,6 +23173,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-78E7B5624F46</t>
         </is>
@@ -22469,7 +23219,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22534,6 +23284,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-C191EF0B2FE3</t>
         </is>
@@ -22570,7 +23330,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22635,6 +23395,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-1F0819D49C79</t>
         </is>
@@ -22671,7 +23441,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22736,6 +23506,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-64AD3556415E</t>
         </is>

--- a/product_upload/packages/7/file.xlsx
+++ b/product_upload/packages/7/file.xlsx
@@ -680,8 +680,16 @@
           <t>7000001282-5-100000073664</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TRISORALEN TABLET 5MG detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1046,8 +1054,16 @@
           <t>7000001034-4.3-100000073652</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ULTRA-K SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1231,8 +1247,16 @@
           <t>28000005519-24.722-100000073713</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ULTRADERM detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1416,8 +1440,16 @@
           <t>28000005519-24.722-100000073712</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ULTRADERM detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1601,8 +1633,16 @@
           <t>7000000227-100-200000016419</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ULTRACEF 500MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1786,8 +1826,16 @@
           <t>14000000704-2.1-100000073712</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UCIDERM -B CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1971,8 +2019,16 @@
           <t>7000000560-2-100000073726</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UCIDERM 2% W-W GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2156,8 +2212,16 @@
           <t>7000000560-2-100000073713</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UCIDERM 2% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2337,8 +2401,16 @@
           <t>7000000560-2-100000073712</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UCIDERM 2 % CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2703,8 +2775,16 @@
           <t>7000000227-50-200000017703</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ULTRACEF 250MG PWD.FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2884,8 +2964,16 @@
           <t>7000001282-5-100000073664</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRISORALEN TABLET 5MG detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3254,8 +3342,16 @@
           <t>7000001145-50-100000073665</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>VERO 50 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3435,8 +3531,16 @@
           <t>7000001145-50-100000073665</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VERO 50 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -4175,8 +4279,16 @@
           <t>7000000797-135-100000073664</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VERINE 135MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4738,8 +4850,16 @@
           <t>7000000758-5-100000073714</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VERSATIS 5% MEDICATED PLASTER detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5705,8 +5825,16 @@
           <t>28000009542-14.4-100000073713</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VICKS VAPORUB OINT detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5882,8 +6010,16 @@
           <t>28000009542-14.4-100000073713</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VICKS VAPORUB OINTCamphor detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6067,8 +6203,16 @@
           <t>14000004727-0.83-200000002007</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VICKS INHALER 0.014 OZ detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6244,8 +6388,16 @@
           <t>21000002404-730-100000073652</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>VICKS DAY QUIL ALCOHOL FREE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6421,8 +6573,16 @@
           <t>14000000972-110-100000073652</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>VICKS 44 E PEDIATRIC ALCOHOL FREE SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6610,8 +6770,16 @@
           <t>7000000946-0.05-200000016498</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VICKS SINEX NASAL SPRAY. detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6984,8 +7152,16 @@
           <t>7000001145-25-100000073665</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>VIAGRA 25MG F.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -8116,8 +8292,16 @@
           <t>7000001127-0.4-100000073652</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>VENTOLIN detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8297,8 +8481,16 @@
           <t>7000000603-50-200000016499</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>VAQTA VACCINE 50 U VIAL detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8486,8 +8678,16 @@
           <t>7000000605-25-200000016499</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>VAQTA 25U SYRINGE I.M detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9250,8 +9450,16 @@
           <t>7000001304-200-200000002007</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>VALOPRA 200 MG-ML SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9431,8 +9639,16 @@
           <t>7000000398-100-100000073664</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>VALONTAN TAB 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -11144,8 +11360,16 @@
           <t>7000001289-300-200000016452</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>VENORUTON 300MG CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11321,8 +11545,16 @@
           <t>7000000721-2-100000073715</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>VAVO 2% SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12276,8 +12508,16 @@
           <t>14000003471-6.25-100000073652</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TRIPOFED SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13229,8 +13469,16 @@
           <t>7000000707-100-100000073854</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TERRELL 100% VAPOUR LIQUID FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13414,8 +13662,16 @@
           <t>7000001215-1.02-100000073712</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TERFINA CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14741,8 +14997,16 @@
           <t>7000000937-75-200000016452</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TABUFLU 75MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15115,8 +15379,16 @@
           <t>7000000806-10-100000073665</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TABIXA 10MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15296,8 +15568,16 @@
           <t>7000000732-300-100000073665</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TABIVIR 300MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15477,8 +15757,16 @@
           <t>7000000732-150-100000073665</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TABIVIR 150MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15851,8 +16139,16 @@
           <t>7000000387-50-100000073998</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TABIFLEX 50MG E.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16036,8 +16332,16 @@
           <t>7000000226-750-100000074010</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TABICLOR MR 750MG F.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16221,8 +16525,16 @@
           <t>7000000226-500-100000073375</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TABICLOR 500MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16406,8 +16718,16 @@
           <t>7000000226-75-100000073649</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TABICLOR 375 MG- 5ML ORAL SUSPNSION detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16587,8 +16907,16 @@
           <t>7000000226-50-100000073649</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TABICLOR 250MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16768,8 +17096,16 @@
           <t>7000000226-25-100000073649</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TABICLOR 125MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17707,8 +18043,16 @@
           <t>14000004740-7.5-100000156088</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TachoSil sealant matrix detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18083,8 +18427,16 @@
           <t>7000000937-75-200000016452</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TAMIFLU 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18260,8 +18612,16 @@
           <t>7000000524-100-100000073664</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ المنتج</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TAMBOCOR 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/7/file.xlsx
+++ b/product_upload/packages/7/file.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21541,7 +21541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21622,40 +21622,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21735,38 +21740,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>49.12</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-19636A66C658</t>
         </is>
@@ -21846,38 +21856,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>482.9</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-84E942455D64</t>
         </is>
@@ -21957,38 +21972,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>365.31</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-16CD00DE0557</t>
         </is>
@@ -22068,38 +22088,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>352.29</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-58A502061BFD</t>
         </is>
@@ -22179,38 +22204,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>231.85</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-59ECCDE298FD</t>
         </is>
@@ -22290,38 +22320,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>494.36</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-BBDC8BD1E523</t>
         </is>
@@ -22401,38 +22436,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>424.32</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-443788E5E988</t>
         </is>
@@ -22512,38 +22552,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>396.9</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-82B7B7580950</t>
         </is>
@@ -22623,38 +22668,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>336.37</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-C5608D94961D</t>
         </is>
@@ -22734,38 +22784,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>265.97</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-3359E601FEB5</t>
         </is>
@@ -22845,38 +22900,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>422.89</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-D84FF2C224FA</t>
         </is>
@@ -22956,38 +23016,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>144.29</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-E09800AA7139</t>
         </is>
@@ -23067,38 +23132,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>121.14</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-7244BD93DD9F</t>
         </is>
@@ -23178,38 +23248,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>272.05</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-7E389C103DB2</t>
         </is>
@@ -23289,38 +23364,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>94.45</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-2B26093B1A96</t>
         </is>
@@ -23400,38 +23480,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>382.99</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-B70C728C4456</t>
         </is>
@@ -23511,38 +23596,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>336.66</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-78E7B5624F46</t>
         </is>
@@ -23622,38 +23712,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>246.19</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-C191EF0B2FE3</t>
         </is>
@@ -23733,38 +23828,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>101.68</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-1F0819D49C79</t>
         </is>
@@ -23844,38 +23944,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>366.74</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-64AD3556415E</t>
         </is>
